--- a/documentation/scrum/Sprint_2_Burndown_Chart.xlsx
+++ b/documentation/scrum/Sprint_2_Burndown_Chart.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://micloud365-my.sharepoint.com/personal/imashai_millenniumitesp_com/Documents/Desktop/MSc BInA/Academics/3-Interactive Visualization/Assesment/Project/group4-interactive-visualisation/documentation/scrum/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{65A0344B-D31D-4040-8B07-A8420AF82D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76BF30B3-02C6-49FB-98E6-72A37A28C709}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{65A0344B-D31D-4040-8B07-A8420AF82D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6258F7FC-60CD-4331-9AC4-6055C1793749}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="380" windowWidth="19200" windowHeight="11280" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint 2 Burndown" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="95">
   <si>
     <t>Day</t>
   </si>
@@ -287,12 +287,6 @@
   </si>
   <si>
     <t>Do not invent actual progress. Use the real Trello checklist count.</t>
-  </si>
-  <si>
-    <t>Projected values</t>
-  </si>
-  <si>
-    <t>Actual Remaining for Day 1-6 (shown in blue) is a PROJECTION assuming each remaining item closes on its planned day in the Task Register, with no slippage. It is not an observed Trello count. Overwrite each blue cell with the real daily count as Sprint 2 actually runs; Completed Today will recalculate automatically.</t>
   </si>
   <si>
     <t>Chart</t>
@@ -384,7 +378,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -393,7 +387,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1048,6 +1041,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1275,8 +1272,8 @@
         <f>IF(OR(D2=""),"",C2-D2)</f>
         <v>12</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>90</v>
+      <c r="F2" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -1296,8 +1293,8 @@
         <f t="shared" ref="E3:E8" si="0">IF(OR(D3="",D2=""),"",D2-D3)</f>
         <v>1</v>
       </c>
-      <c r="F3" s="6" t="s">
-        <v>91</v>
+      <c r="F3" s="2" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -1317,8 +1314,8 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>92</v>
+      <c r="F4" s="2" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -1338,8 +1335,8 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>93</v>
+      <c r="F5" s="2" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -1359,8 +1356,8 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F6" s="6" t="s">
-        <v>94</v>
+      <c r="F6" s="2" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -1380,8 +1377,8 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>95</v>
+      <c r="F7" s="2" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -1401,8 +1398,8 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F8" s="6" t="s">
-        <v>96</v>
+      <c r="F8" s="2" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -1955,7 +1952,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -2018,7 +2015,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>84</v>
       </c>
@@ -2032,14 +2029,6 @@
       </c>
       <c r="B9" s="5" t="s">
         <v>87</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/documentation/scrum/Sprint_2_Burndown_Chart.xlsx
+++ b/documentation/scrum/Sprint_2_Burndown_Chart.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://micloud365-my.sharepoint.com/personal/imashai_millenniumitesp_com/Documents/Desktop/MSc BInA/Academics/3-Interactive Visualization/Assesment/Project/group4-interactive-visualisation/documentation/scrum/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{65A0344B-D31D-4040-8B07-A8420AF82D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6258F7FC-60CD-4331-9AC4-6055C1793749}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{65A0344B-D31D-4040-8B07-A8420AF82D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{956537DC-4805-4D38-B12C-C3CF959A6390}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="11280" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint 2 Burndown" sheetId="1" r:id="rId1"/>
@@ -115,9 +115,6 @@
     <t>To Do</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>All</t>
   </si>
   <si>
@@ -320,6 +317,9 @@
   </si>
   <si>
     <t>Sprint end. Progress-review prep for Meeting 03 (S2-19) closed today, per actual Trello count.</t>
+  </si>
+  <si>
+    <t>Yes</t>
   </si>
 </sst>
 </file>
@@ -1273,7 +1273,7 @@
         <v>12</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -1294,7 +1294,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -1315,7 +1315,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -1336,7 +1336,7 @@
         <v>2</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -1357,7 +1357,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -1378,7 +1378,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -1399,7 +1399,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1467,10 +1467,10 @@
         <v>25</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="H2" s="2">
         <v>0</v>
@@ -1478,13 +1478,13 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>24</v>
@@ -1493,10 +1493,10 @@
         <v>25</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="H3" s="2">
         <v>0</v>
@@ -1504,13 +1504,13 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>24</v>
@@ -1519,10 +1519,10 @@
         <v>25</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="H4" s="2">
         <v>0</v>
@@ -1530,13 +1530,13 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>24</v>
@@ -1545,10 +1545,10 @@
         <v>25</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="H5" s="2">
         <v>0</v>
@@ -1556,13 +1556,13 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>24</v>
@@ -1571,10 +1571,10 @@
         <v>25</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H6" s="2">
         <v>0</v>
@@ -1582,13 +1582,13 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>24</v>
@@ -1597,10 +1597,10 @@
         <v>25</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H7" s="2">
         <v>0</v>
@@ -1608,13 +1608,13 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>24</v>
@@ -1623,10 +1623,10 @@
         <v>25</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H8" s="2">
         <v>0</v>
@@ -1634,13 +1634,13 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>24</v>
@@ -1649,10 +1649,10 @@
         <v>25</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H9" s="2">
         <v>0</v>
@@ -1660,13 +1660,13 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>24</v>
@@ -1675,10 +1675,10 @@
         <v>25</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H10" s="2">
         <v>0</v>
@@ -1686,13 +1686,13 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>24</v>
@@ -1701,10 +1701,10 @@
         <v>25</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H11" s="2">
         <v>0</v>
@@ -1712,13 +1712,13 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>24</v>
@@ -1727,10 +1727,10 @@
         <v>25</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H12" s="2">
         <v>0</v>
@@ -1738,13 +1738,13 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>24</v>
@@ -1753,10 +1753,10 @@
         <v>25</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H13" s="2">
         <v>0</v>
@@ -1764,13 +1764,13 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>24</v>
@@ -1779,10 +1779,10 @@
         <v>25</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H14" s="2">
         <v>1</v>
@@ -1790,13 +1790,13 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>24</v>
@@ -1805,10 +1805,10 @@
         <v>25</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H15" s="2">
         <v>2</v>
@@ -1816,13 +1816,13 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>24</v>
@@ -1831,10 +1831,10 @@
         <v>25</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H16" s="2">
         <v>3</v>
@@ -1842,13 +1842,13 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>24</v>
@@ -1857,10 +1857,10 @@
         <v>25</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H17" s="2">
         <v>3</v>
@@ -1868,13 +1868,13 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>24</v>
@@ -1883,10 +1883,10 @@
         <v>25</v>
       </c>
       <c r="F18" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="H18" s="2">
         <v>4</v>
@@ -1894,13 +1894,13 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>68</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>24</v>
@@ -1909,10 +1909,10 @@
         <v>25</v>
       </c>
       <c r="F19" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="H19" s="2">
         <v>5</v>
@@ -1920,13 +1920,13 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>24</v>
@@ -1935,10 +1935,10 @@
         <v>25</v>
       </c>
       <c r="F20" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="H20" s="2">
         <v>6</v>
@@ -1961,42 +1961,42 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>73</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>75</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>77</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>79</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -2004,31 +2004,31 @@
         <v>4</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>82</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>86</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>87</v>
       </c>
     </row>
   </sheetData>
